--- a/Assets/StreamingAssets/DataTable.xlsx
+++ b/Assets/StreamingAssets/DataTable.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SWProject\KGSDemo\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\KGSDemo\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D76583D-DFF6-4B8E-B1B3-47C9AE342A69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32B29D4B-D030-4C51-A9DE-42F234235A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="55035" yWindow="1680" windowWidth="28710" windowHeight="15345" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Notice" sheetId="3" r:id="rId1"/>
@@ -160,7 +160,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="283">
   <si>
     <t>Scenario Sheet</t>
   </si>
@@ -1145,6 +1145,10 @@
   </si>
   <si>
     <t>DialogueID</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T1011</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1350,10 +1354,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -18275,8 +18279,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="15143513" y="6569156"/>
-          <a:ext cx="10278959" cy="4751615"/>
+          <a:off x="15143513" y="6732442"/>
+          <a:ext cx="10278959" cy="4751614"/>
           <a:chOff x="15087600" y="2219325"/>
           <a:chExt cx="10353675" cy="4819650"/>
         </a:xfrm>
@@ -18869,11 +18873,11 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:4">
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="23"/>
-      <c r="D3" s="23"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
     </row>
     <row r="4" spans="2:4">
       <c r="B4" s="8" t="s">
@@ -18917,10 +18921,10 @@
       </c>
     </row>
     <row r="28" spans="2:4">
-      <c r="C28" s="23" t="s">
+      <c r="C28" s="24" t="s">
         <v>10</v>
       </c>
-      <c r="D28" s="23"/>
+      <c r="D28" s="24"/>
     </row>
     <row r="29" spans="2:4">
       <c r="C29" s="6" t="s">
@@ -20307,37 +20311,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="23" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="24" t="s">
+      <c r="D1" s="23" t="s">
         <v>279</v>
       </c>
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="23" t="s">
         <v>260</v>
       </c>
-      <c r="F1" s="24" t="s">
+      <c r="F1" s="23" t="s">
         <v>261</v>
       </c>
-      <c r="G1" s="24" t="s">
+      <c r="G1" s="23" t="s">
         <v>262</v>
       </c>
-      <c r="H1" s="24" t="s">
+      <c r="H1" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>208</v>
+        <v>282</v>
       </c>
       <c r="B2" t="s">
         <v>196</v>
@@ -21492,7 +21496,7 @@
       </c>
       <c r="E6" s="13"/>
     </row>
-    <row r="7" spans="1:5" ht="27">
+    <row r="7" spans="1:5" ht="30">
       <c r="A7" s="10"/>
       <c r="B7" s="10" t="s">
         <v>99</v>
@@ -21534,7 +21538,7 @@
       </c>
       <c r="E10" s="12"/>
     </row>
-    <row r="11" spans="1:5" ht="27">
+    <row r="11" spans="1:5" ht="30">
       <c r="A11" s="10"/>
       <c r="B11" s="10" t="s">
         <v>99</v>
@@ -21547,7 +21551,7 @@
       </c>
       <c r="E11" s="12"/>
     </row>
-    <row r="12" spans="1:5" ht="27">
+    <row r="12" spans="1:5" ht="30">
       <c r="A12" s="10"/>
       <c r="B12" s="10"/>
       <c r="C12" s="10" t="s">
@@ -21569,7 +21573,7 @@
       </c>
       <c r="E13" s="12"/>
     </row>
-    <row r="14" spans="1:5" ht="27">
+    <row r="14" spans="1:5" ht="30">
       <c r="A14" s="10"/>
       <c r="B14" s="10"/>
       <c r="C14" s="10" t="s">
@@ -21736,18 +21740,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -21889,14 +21893,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C71F4C32-817E-493F-985A-087FE5166A5D}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{27FB351B-A7F5-4D01-B236-06985937BBDC}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -21908,6 +21904,14 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C71F4C32-817E-493F-985A-087FE5166A5D}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
